--- a/build/report-suite/questions-2026-08-06/Questions-for-Chris-Ward_Report-Suite_2026-08-06.xlsx
+++ b/build/report-suite/questions-2026-08-06/Questions-for-Chris-Ward_Report-Suite_2026-08-06.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,6 +34,10 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
     </font>
   </fonts>
   <fills count="4">
@@ -68,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -80,6 +84,9 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -459,73 +466,81 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>*** SUPERSEDED 2026-08-06 — DO NOT SEND THIS FILE. The version to send is Questions-for-Chris-Ward_Report-Suite_Friendly-Version_2026-08-06.xlsx (plain-language twin Questions-for-Chris-Ward_Report-Suite_Friendly-Version_2026-08-06.md) in this same folder: same substance, reordered by what to do first and rewritten to read easily. This file is kept only as the record of what was verified and when.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Needed first - the Location column - Report Suite - Chris Ward - 2026-08-06</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Needed first, please - this is a one-line confirmation and it releases seven tests that are on hold today. Everything else on this sheet can wait until you have a spare ten minutes. Thank you - your last round of answers landed well and most of the reporting work moved straight away. This sheet is the rest of what is genuinely still open. Every question says which project and which report it is about, because we know you look after more than one thing here.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Topic</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>What happens now</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>The question</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Options</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Your answer</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="6" ht="300" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>ONE CONFIRMATION - IT RELEASES SEVEN HELD TESTS</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="300" customHeight="1">
-      <c r="A6" s="6" t="n">
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Report Suite - the Location column - all six reports (the "show or hide columns" story on each report, under epic SV-8582)</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>This is a one-line confirmation rather than a fresh decision, and it is the only thing holding seven of our tests.
 You have already decided this. The note recording your decision appears in every one of the six written descriptions, and it says the same thing each time: anyone who can see more than one location gets the Location column, it is on by default, and they can switch it on or off themselves from the list of columns. Someone who can see only one location never sees it at all.
@@ -533,19 +548,19 @@
 Why we are asking: we do not want to release seven tests on our own reading of a note. One word from you and they go.</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>Is this right - anyone who can see more than one location gets the Location column, on by default, and can switch it on or off themselves?</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>A) Yes, that is the rule - it is an access thing, not a picking thing, and the person can switch it on or off whenever they like. (Then the older sentences on the third tab are just leftovers to delete, and our seven tests come off hold the same day.)
 B) No - the column should appear and disappear on its own depending on how many locations are picked, and the person should not be able to switch it. (Then the newer note in all six descriptions is the one that needs removing, and we rewrite the seven tests.)
 C) Something else, or it should differ between reports - please describe it.</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
